--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/22.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/22.xlsx
@@ -426,13 +426,13 @@
         <v>-21.62126998203022</v>
       </c>
       <c r="E2">
-        <v>-27.69947753601515</v>
+        <v>-28.89771175844472</v>
       </c>
       <c r="F2">
-        <v>-4.919220063889034</v>
+        <v>-5.256551007583552</v>
       </c>
       <c r="G2">
-        <v>-19.42876528426611</v>
+        <v>-20.07503343171494</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.90950500031256</v>
       </c>
       <c r="E3">
-        <v>-28.28822897022638</v>
+        <v>-27.81061534511139</v>
       </c>
       <c r="F3">
-        <v>-4.435408992663691</v>
+        <v>-5.354737606928967</v>
       </c>
       <c r="G3">
-        <v>-19.65940437089606</v>
+        <v>-19.37367946176541</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.09312680707396</v>
       </c>
       <c r="E4">
-        <v>-29.67964110111216</v>
+        <v>-28.45598176136652</v>
       </c>
       <c r="F4">
-        <v>-4.7256056809029</v>
+        <v>-5.940502122019597</v>
       </c>
       <c r="G4">
-        <v>-18.69949679432945</v>
+        <v>-19.84285328613646</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.28966605241155</v>
       </c>
       <c r="E5">
-        <v>-29.08050361176434</v>
+        <v>-31.31281260960844</v>
       </c>
       <c r="F5">
-        <v>-5.017523857472192</v>
+        <v>-5.900703592364604</v>
       </c>
       <c r="G5">
-        <v>-18.27647859586692</v>
+        <v>-19.25504606236563</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.52525311912642</v>
       </c>
       <c r="E6">
-        <v>-30.49443131541626</v>
+        <v>-30.441735727626</v>
       </c>
       <c r="F6">
-        <v>-4.667703808928518</v>
+        <v>-5.67392561565621</v>
       </c>
       <c r="G6">
-        <v>-18.57128929723009</v>
+        <v>-20.3948884100827</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.83131368616714</v>
       </c>
       <c r="E7">
-        <v>-29.27989232232206</v>
+        <v>-30.14037031088954</v>
       </c>
       <c r="F7">
-        <v>-5.142285833931638</v>
+        <v>-5.507662625682673</v>
       </c>
       <c r="G7">
-        <v>-17.76202478488248</v>
+        <v>-19.64276225847014</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.23207811011716</v>
       </c>
       <c r="E8">
-        <v>-30.94508693476358</v>
+        <v>-31.14805993249838</v>
       </c>
       <c r="F8">
-        <v>-4.982367169855351</v>
+        <v>-5.754885453906432</v>
       </c>
       <c r="G8">
-        <v>-18.98267920448594</v>
+        <v>-17.59675904101653</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.7469206294106</v>
       </c>
       <c r="E9">
-        <v>-31.82810540270424</v>
+        <v>-31.86671517209364</v>
       </c>
       <c r="F9">
-        <v>-4.970254195161113</v>
+        <v>-5.123907718635921</v>
       </c>
       <c r="G9">
-        <v>-18.20602356570015</v>
+        <v>-17.76122694340752</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.35744576873764</v>
       </c>
       <c r="E10">
-        <v>-31.39735695509464</v>
+        <v>-30.95031732224244</v>
       </c>
       <c r="F10">
-        <v>-4.882630122418721</v>
+        <v>-5.786682309423668</v>
       </c>
       <c r="G10">
-        <v>-17.32691978465607</v>
+        <v>-18.02699753930021</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.0576341497086</v>
       </c>
       <c r="E11">
-        <v>-31.88431282208744</v>
+        <v>-31.57853214319351</v>
       </c>
       <c r="F11">
-        <v>-4.041246762193628</v>
+        <v>-5.388810247846688</v>
       </c>
       <c r="G11">
-        <v>-17.25578278210821</v>
+        <v>-18.63855627204255</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.81555352012298</v>
       </c>
       <c r="E12">
-        <v>-32.00553101432477</v>
+        <v>-29.91881472006427</v>
       </c>
       <c r="F12">
-        <v>-4.661194777616062</v>
+        <v>-4.722191210949212</v>
       </c>
       <c r="G12">
-        <v>-17.72395351118087</v>
+        <v>-16.25366409464313</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.57882312450115</v>
       </c>
       <c r="E13">
-        <v>-33.17619588699564</v>
+        <v>-34.36936727548465</v>
       </c>
       <c r="F13">
-        <v>-4.788891361136818</v>
+        <v>-5.40755182365</v>
       </c>
       <c r="G13">
-        <v>-16.17021848378026</v>
+        <v>-16.03989389280854</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.31856339832521</v>
       </c>
       <c r="E14">
-        <v>-33.37203880240536</v>
+        <v>-33.69034524040452</v>
       </c>
       <c r="F14">
-        <v>-3.935969119611834</v>
+        <v>-5.097545349967516</v>
       </c>
       <c r="G14">
-        <v>-16.45935822063467</v>
+        <v>-16.90798017829792</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.99861733431072</v>
       </c>
       <c r="E15">
-        <v>-33.92504925551106</v>
+        <v>-34.2564543045774</v>
       </c>
       <c r="F15">
-        <v>-4.390419866870845</v>
+        <v>-5.311184110548466</v>
       </c>
       <c r="G15">
-        <v>-15.69001392167235</v>
+        <v>-15.2782648202255</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.59577538997623</v>
       </c>
       <c r="E16">
-        <v>-34.90432949543277</v>
+        <v>-35.75885480491717</v>
       </c>
       <c r="F16">
-        <v>-4.271710814420208</v>
+        <v>-5.064989899316785</v>
       </c>
       <c r="G16">
-        <v>-15.57248293393715</v>
+        <v>-17.31504982362501</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.1182408590213</v>
       </c>
       <c r="E17">
-        <v>-33.91057851681955</v>
+        <v>-36.11393471609561</v>
       </c>
       <c r="F17">
-        <v>-4.086292901399431</v>
+        <v>-4.707144421046622</v>
       </c>
       <c r="G17">
-        <v>-15.19065950889254</v>
+        <v>-15.36172036272499</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.57109457279787</v>
       </c>
       <c r="E18">
-        <v>-35.7016035722752</v>
+        <v>-35.91190364095441</v>
       </c>
       <c r="F18">
-        <v>-3.844434876964222</v>
+        <v>-4.653115501888448</v>
       </c>
       <c r="G18">
-        <v>-14.84191836542186</v>
+        <v>-15.30989211703493</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.97254835554752</v>
       </c>
       <c r="E19">
-        <v>-36.48187549345582</v>
+        <v>-36.60499111630236</v>
       </c>
       <c r="F19">
-        <v>-3.816993212714445</v>
+        <v>-4.501749641608492</v>
       </c>
       <c r="G19">
-        <v>-14.75391744389696</v>
+        <v>-14.98987988775405</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.35292140145965</v>
       </c>
       <c r="E20">
-        <v>-36.78985474648049</v>
+        <v>-35.70529880706545</v>
       </c>
       <c r="F20">
-        <v>-3.671855275946955</v>
+        <v>-4.379862091385568</v>
       </c>
       <c r="G20">
-        <v>-15.08015846460997</v>
+        <v>-14.70977462967631</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.73158047932295</v>
       </c>
       <c r="E21">
-        <v>-36.84425077626062</v>
+        <v>-38.21864263758857</v>
       </c>
       <c r="F21">
-        <v>-3.419271603199433</v>
+        <v>-4.509718057922025</v>
       </c>
       <c r="G21">
-        <v>-15.99391041526806</v>
+        <v>-15.33541807841548</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.14322274826061</v>
       </c>
       <c r="E22">
-        <v>-37.20864122999883</v>
+        <v>-38.43009746713974</v>
       </c>
       <c r="F22">
-        <v>-3.467594429944279</v>
+        <v>-4.498224312240723</v>
       </c>
       <c r="G22">
-        <v>-14.79702074681827</v>
+        <v>-15.3591083422945</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.62112710385271</v>
       </c>
       <c r="E23">
-        <v>-37.72139581341333</v>
+        <v>-38.71497018154025</v>
       </c>
       <c r="F23">
-        <v>-2.913547585075112</v>
+        <v>-3.969204771953246</v>
       </c>
       <c r="G23">
-        <v>-15.25376347268936</v>
+        <v>-15.05691512437875</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.1817692392994</v>
       </c>
       <c r="E24">
-        <v>-39.05806775049439</v>
+        <v>-39.11230075521026</v>
       </c>
       <c r="F24">
-        <v>-2.821717189421313</v>
+        <v>-4.207238146602668</v>
       </c>
       <c r="G24">
-        <v>-15.25694821749813</v>
+        <v>-15.08310816068546</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.849910906461639</v>
       </c>
       <c r="E25">
-        <v>-38.55888047520687</v>
+        <v>-40.23414867807845</v>
       </c>
       <c r="F25">
-        <v>-2.975877498789062</v>
+        <v>-4.112188076822781</v>
       </c>
       <c r="G25">
-        <v>-14.59515361147013</v>
+        <v>-15.72531592403037</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.632666236674687</v>
       </c>
       <c r="E26">
-        <v>-37.19495391731064</v>
+        <v>-39.67910720438032</v>
       </c>
       <c r="F26">
-        <v>-2.924729340691072</v>
+        <v>-4.333111884614753</v>
       </c>
       <c r="G26">
-        <v>-14.14427717229463</v>
+        <v>-14.8867646705696</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.518902214072176</v>
       </c>
       <c r="E27">
-        <v>-39.00863719246367</v>
+        <v>-37.4433044888393</v>
       </c>
       <c r="F27">
-        <v>-2.922381496671433</v>
+        <v>-4.185911170892402</v>
       </c>
       <c r="G27">
-        <v>-14.51829433095764</v>
+        <v>-15.49301825408525</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.509542646018682</v>
       </c>
       <c r="E28">
-        <v>-37.74311890322813</v>
+        <v>-39.05819681200362</v>
       </c>
       <c r="F28">
-        <v>-2.889008061915377</v>
+        <v>-4.564214170325254</v>
       </c>
       <c r="G28">
-        <v>-13.80583348072386</v>
+        <v>-15.00913898642876</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.588094572593944</v>
       </c>
       <c r="E29">
-        <v>-39.32013506979229</v>
+        <v>-40.24343657826818</v>
       </c>
       <c r="F29">
-        <v>-3.33792296514697</v>
+        <v>-4.722340079305264</v>
       </c>
       <c r="G29">
-        <v>-14.1235961943108</v>
+        <v>-15.19564684574745</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.73580687817419</v>
       </c>
       <c r="E30">
-        <v>-38.71541397199301</v>
+        <v>-38.43858382743011</v>
       </c>
       <c r="F30">
-        <v>-3.067728482619761</v>
+        <v>-4.220653719412356</v>
       </c>
       <c r="G30">
-        <v>-15.01786723974305</v>
+        <v>-15.77974956905984</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.944265355560955</v>
       </c>
       <c r="E31">
-        <v>-37.69183393509126</v>
+        <v>-41.25127563951926</v>
       </c>
       <c r="F31">
-        <v>-3.196863071111736</v>
+        <v>-3.526212928845397</v>
       </c>
       <c r="G31">
-        <v>-14.68837691858323</v>
+        <v>-16.51225908307945</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.19152431408256</v>
       </c>
       <c r="E32">
-        <v>-37.90917125237839</v>
+        <v>-38.76892468510464</v>
       </c>
       <c r="F32">
-        <v>-3.456776134835912</v>
+        <v>-3.979039585688125</v>
       </c>
       <c r="G32">
-        <v>-15.59529259270273</v>
+        <v>-12.7289097062534</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.46599044538681</v>
       </c>
       <c r="E33">
-        <v>-38.00562774874177</v>
+        <v>-38.62316669221976</v>
       </c>
       <c r="F33">
-        <v>-3.23031014819286</v>
+        <v>-4.639630246018481</v>
       </c>
       <c r="G33">
-        <v>-14.3602339894579</v>
+        <v>-16.08476833759336</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.76186239680749</v>
       </c>
       <c r="E34">
-        <v>-36.80171029143256</v>
+        <v>-38.61332631820109</v>
       </c>
       <c r="F34">
-        <v>-2.948682892662093</v>
+        <v>-3.508424744003181</v>
       </c>
       <c r="G34">
-        <v>-14.48465422246033</v>
+        <v>-15.1796006315186</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.06269376778771</v>
       </c>
       <c r="E35">
-        <v>-37.01573050150908</v>
+        <v>-38.23909775468122</v>
       </c>
       <c r="F35">
-        <v>-3.279618040017109</v>
+        <v>-4.374263690974489</v>
       </c>
       <c r="G35">
-        <v>-14.87736768705638</v>
+        <v>-15.23322981398202</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.37034240747144</v>
       </c>
       <c r="E36">
-        <v>-36.80606668342794</v>
+        <v>-38.19990834061884</v>
       </c>
       <c r="F36">
-        <v>-3.167189965227105</v>
+        <v>-4.176968775440874</v>
       </c>
       <c r="G36">
-        <v>-14.27797189862532</v>
+        <v>-15.49729878946753</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.68454533282319</v>
       </c>
       <c r="E37">
-        <v>-36.38629072833892</v>
+        <v>-38.31647579005028</v>
       </c>
       <c r="F37">
-        <v>-3.275629476669075</v>
+        <v>-4.319595746479435</v>
       </c>
       <c r="G37">
-        <v>-14.15557606422016</v>
+        <v>-14.55049104159982</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.99739946087807</v>
       </c>
       <c r="E38">
-        <v>-36.07503512436972</v>
+        <v>-38.28780828534472</v>
       </c>
       <c r="F38">
-        <v>-3.21384277408412</v>
+        <v>-4.02313312578579</v>
       </c>
       <c r="G38">
-        <v>-14.33748392051203</v>
+        <v>-14.76725232132914</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.31793053629784</v>
       </c>
       <c r="E39">
-        <v>-35.87097982134708</v>
+        <v>-35.66607316521102</v>
       </c>
       <c r="F39">
-        <v>-3.281065547223821</v>
+        <v>-4.040158756229721</v>
       </c>
       <c r="G39">
-        <v>-14.47637123752108</v>
+        <v>-14.28434469878842</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.64440800346777</v>
       </c>
       <c r="E40">
-        <v>-35.33901092271803</v>
+        <v>-35.95738536965044</v>
       </c>
       <c r="F40">
-        <v>-3.429507094530918</v>
+        <v>-3.814281116334255</v>
       </c>
       <c r="G40">
-        <v>-14.10302446432977</v>
+        <v>-15.96286080865524</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.96924307476167</v>
       </c>
       <c r="E41">
-        <v>-35.16471222239981</v>
+        <v>-33.91844221193386</v>
       </c>
       <c r="F41">
-        <v>-3.358599829578948</v>
+        <v>-3.932712228396733</v>
       </c>
       <c r="G41">
-        <v>-13.97359703119919</v>
+        <v>-14.68285161807819</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.29773070220096</v>
       </c>
       <c r="E42">
-        <v>-34.67617591797832</v>
+        <v>-34.52400560589857</v>
       </c>
       <c r="F42">
-        <v>-2.955604479365522</v>
+        <v>-3.866759587401214</v>
       </c>
       <c r="G42">
-        <v>-13.83955800813241</v>
+        <v>-14.38511604973107</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.61979173732257</v>
       </c>
       <c r="E43">
-        <v>-34.60349843862922</v>
+        <v>-35.30687913539661</v>
       </c>
       <c r="F43">
-        <v>-2.787904276273723</v>
+        <v>-3.605906594216225</v>
       </c>
       <c r="G43">
-        <v>-15.02268739404823</v>
+        <v>-14.36169725058626</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.92482253578173</v>
       </c>
       <c r="E44">
-        <v>-32.80851323265387</v>
+        <v>-34.70915000146518</v>
       </c>
       <c r="F44">
-        <v>-2.819945814354894</v>
+        <v>-4.201269950860334</v>
       </c>
       <c r="G44">
-        <v>-14.57900477032956</v>
+        <v>-15.20889564899561</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.21188260420503</v>
       </c>
       <c r="E45">
-        <v>-33.8088893687403</v>
+        <v>-33.8560602182412</v>
       </c>
       <c r="F45">
-        <v>-2.759307298558633</v>
+        <v>-3.7608080779524</v>
       </c>
       <c r="G45">
-        <v>-14.15457462419453</v>
+        <v>-15.19536710464938</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.46693112278559</v>
       </c>
       <c r="E46">
-        <v>-33.89226989640654</v>
+        <v>-32.72335301470262</v>
       </c>
       <c r="F46">
-        <v>-2.991787408415567</v>
+        <v>-4.657172956443803</v>
       </c>
       <c r="G46">
-        <v>-14.63343510481349</v>
+        <v>-15.90691093376878</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.6847497794113</v>
       </c>
       <c r="E47">
-        <v>-32.42088038607129</v>
+        <v>-34.123973797483</v>
       </c>
       <c r="F47">
-        <v>-3.08081385274608</v>
+        <v>-4.156261820596503</v>
       </c>
       <c r="G47">
-        <v>-14.72018629539732</v>
+        <v>-14.24616086653847</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.86512433648567</v>
       </c>
       <c r="E48">
-        <v>-32.62998946608648</v>
+        <v>-32.6754055319094</v>
       </c>
       <c r="F48">
-        <v>-3.107861174222912</v>
+        <v>-4.042467799454433</v>
       </c>
       <c r="G48">
-        <v>-14.68546860432699</v>
+        <v>-16.19090277230962</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.99535494658061</v>
       </c>
       <c r="E49">
-        <v>-31.96865565048031</v>
+        <v>-35.27963583576646</v>
       </c>
       <c r="F49">
-        <v>-3.073425072797597</v>
+        <v>-4.187697591165018</v>
       </c>
       <c r="G49">
-        <v>-15.31483310625229</v>
+        <v>-16.1603712660737</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-15.07875573658597</v>
       </c>
       <c r="E50">
-        <v>-31.91407621750286</v>
+        <v>-31.66198286220686</v>
       </c>
       <c r="F50">
-        <v>-3.465001903360704</v>
+        <v>-4.224896467559818</v>
       </c>
       <c r="G50">
-        <v>-14.29190929534566</v>
+        <v>-16.49096399889808</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-15.11784840086212</v>
       </c>
       <c r="E51">
-        <v>-31.25775768686018</v>
+        <v>-31.68735816630884</v>
       </c>
       <c r="F51">
-        <v>-3.240405481550829</v>
+        <v>-4.021140823744167</v>
       </c>
       <c r="G51">
-        <v>-15.15180198062534</v>
+        <v>-15.7512954301498</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-15.10539991153969</v>
       </c>
       <c r="E52">
-        <v>-31.40622144296465</v>
+        <v>-31.35588519013239</v>
       </c>
       <c r="F52">
-        <v>-3.098265500081265</v>
+        <v>-3.839194394090033</v>
       </c>
       <c r="G52">
-        <v>-15.23072042046326</v>
+        <v>-16.55198728482347</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.05387266426669</v>
       </c>
       <c r="E53">
-        <v>-31.23356657871121</v>
+        <v>-32.7120657932385</v>
       </c>
       <c r="F53">
-        <v>-2.998617140175899</v>
+        <v>-4.46645121231222</v>
       </c>
       <c r="G53">
-        <v>-14.61306366283758</v>
+        <v>-15.70836262032376</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-14.96958357583938</v>
       </c>
       <c r="E54">
-        <v>-30.66049951422554</v>
+        <v>-30.03995366400646</v>
       </c>
       <c r="F54">
-        <v>-3.149433454503198</v>
+        <v>-4.588494757567815</v>
       </c>
       <c r="G54">
-        <v>-15.93678860726071</v>
+        <v>-14.82393051623423</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-14.85224941324693</v>
       </c>
       <c r="E55">
-        <v>-31.02548772653276</v>
+        <v>-31.72189004485433</v>
       </c>
       <c r="F55">
-        <v>-3.315617259180963</v>
+        <v>-3.904931651081051</v>
       </c>
       <c r="G55">
-        <v>-15.9638225221344</v>
+        <v>-15.92728899683577</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.72163213039457</v>
       </c>
       <c r="E56">
-        <v>-28.88315271451006</v>
+        <v>-32.17350117221727</v>
       </c>
       <c r="F56">
-        <v>-3.35884213658401</v>
+        <v>-3.945096808655469</v>
       </c>
       <c r="G56">
-        <v>-15.14728143069147</v>
+        <v>-16.53081965664537</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.58611056555346</v>
       </c>
       <c r="E57">
-        <v>-29.70350615913258</v>
+        <v>-29.6000780770344</v>
       </c>
       <c r="F57">
-        <v>-3.362066561827844</v>
+        <v>-4.345973952206995</v>
       </c>
       <c r="G57">
-        <v>-15.04177599962766</v>
+        <v>-16.47090540347564</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.45210805428386</v>
       </c>
       <c r="E58">
-        <v>-29.73034642457604</v>
+        <v>-30.22411085223938</v>
       </c>
       <c r="F58">
-        <v>-3.016883604204578</v>
+        <v>-3.83509417947496</v>
       </c>
       <c r="G58">
-        <v>-15.94551520530223</v>
+        <v>-16.67342140574948</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.34067394428926</v>
       </c>
       <c r="E59">
-        <v>-30.00224732518159</v>
+        <v>-30.40714724315541</v>
       </c>
       <c r="F59">
-        <v>-3.178104866396314</v>
+        <v>-4.771309058063609</v>
       </c>
       <c r="G59">
-        <v>-16.58554628495506</v>
+        <v>-16.81990476949838</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.25468071942101</v>
       </c>
       <c r="E60">
-        <v>-28.35322162918446</v>
+        <v>-28.65151221206971</v>
       </c>
       <c r="F60">
-        <v>-3.080839983893684</v>
+        <v>-4.247709751271723</v>
       </c>
       <c r="G60">
-        <v>-15.38594362443584</v>
+        <v>-16.82909980973371</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.20033851133482</v>
       </c>
       <c r="E61">
-        <v>-29.75325823881785</v>
+        <v>-29.70534245534269</v>
       </c>
       <c r="F61">
-        <v>-3.295937337622755</v>
+        <v>-4.62507678050855</v>
       </c>
       <c r="G61">
-        <v>-15.80897175453499</v>
+        <v>-16.78573662898756</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.18849718182629</v>
       </c>
       <c r="E62">
-        <v>-28.44573835316117</v>
+        <v>-28.7348723616029</v>
       </c>
       <c r="F62">
-        <v>-2.815570034910535</v>
+        <v>-4.749176767895343</v>
       </c>
       <c r="G62">
-        <v>-15.62782863426268</v>
+        <v>-18.27637100313689</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.20932865539993</v>
       </c>
       <c r="E63">
-        <v>-27.88193428225819</v>
+        <v>-29.88769051820956</v>
       </c>
       <c r="F63">
-        <v>-3.431453469100993</v>
+        <v>-4.180879737199051</v>
       </c>
       <c r="G63">
-        <v>-16.1987868365114</v>
+        <v>-18.26432061737394</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.26273395004566</v>
       </c>
       <c r="E64">
-        <v>-27.55643662753486</v>
+        <v>-30.41610230050558</v>
       </c>
       <c r="F64">
-        <v>-3.256586204888873</v>
+        <v>-4.426629718921452</v>
       </c>
       <c r="G64">
-        <v>-16.47025819182272</v>
+        <v>-18.75735188817375</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.34476176873259</v>
       </c>
       <c r="E65">
-        <v>-27.69434224649045</v>
+        <v>-31.04799424235089</v>
       </c>
       <c r="F65">
-        <v>-3.715350175208584</v>
+        <v>-4.060204513854397</v>
       </c>
       <c r="G65">
-        <v>-15.91880241334585</v>
+        <v>-15.87935726324543</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.43556006388008</v>
       </c>
       <c r="E66">
-        <v>-28.37200121089427</v>
+        <v>-30.93722550388626</v>
       </c>
       <c r="F66">
-        <v>-3.192646454111879</v>
+        <v>-4.478756607275184</v>
       </c>
       <c r="G66">
-        <v>-17.20639606375336</v>
+        <v>-16.64102771764771</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.53522959572629</v>
       </c>
       <c r="E67">
-        <v>-28.33236800637914</v>
+        <v>-30.18491011699199</v>
       </c>
       <c r="F67">
-        <v>-3.876930938643124</v>
+        <v>-4.841172660817305</v>
       </c>
       <c r="G67">
-        <v>-16.95787837593858</v>
+        <v>-17.74223268837595</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.63663993687238</v>
       </c>
       <c r="E68">
-        <v>-28.34065511381318</v>
+        <v>-30.41593021849329</v>
       </c>
       <c r="F68">
-        <v>-3.85760022423927</v>
+        <v>-4.712023818972091</v>
       </c>
       <c r="G68">
-        <v>-15.28963985469844</v>
+        <v>-17.2979442348236</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.72641888333505</v>
       </c>
       <c r="E69">
-        <v>-28.66185071822922</v>
+        <v>-30.12472443319304</v>
       </c>
       <c r="F69">
-        <v>-3.421949649902441</v>
+        <v>-4.501169213390483</v>
       </c>
       <c r="G69">
-        <v>-16.59702394633972</v>
+        <v>-16.14311835799579</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.81322098307527</v>
       </c>
       <c r="E70">
-        <v>-28.76158582977415</v>
+        <v>-28.65428816663641</v>
       </c>
       <c r="F70">
-        <v>-3.82349907661507</v>
+        <v>-4.738322839403879</v>
       </c>
       <c r="G70">
-        <v>-17.17217164396838</v>
+        <v>-16.2141759074507</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.89493898546566</v>
       </c>
       <c r="E71">
-        <v>-28.34973470419856</v>
+        <v>-29.16389546061558</v>
       </c>
       <c r="F71">
-        <v>-4.279493145288678</v>
+        <v>-4.488890741428081</v>
       </c>
       <c r="G71">
-        <v>-17.0964892623951</v>
+        <v>-16.84263000935271</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.96798352284827</v>
       </c>
       <c r="E72">
-        <v>-28.44323410703493</v>
+        <v>-27.97903382193066</v>
       </c>
       <c r="F72">
-        <v>-4.059371484542876</v>
+        <v>-4.146279722211489</v>
       </c>
       <c r="G72">
-        <v>-16.71070476961275</v>
+        <v>-17.06339208336624</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.0441905399995</v>
       </c>
       <c r="E73">
-        <v>-28.89015826379993</v>
+        <v>-31.68167040295521</v>
       </c>
       <c r="F73">
-        <v>-4.404385777486148</v>
+        <v>-4.814560858467218</v>
       </c>
       <c r="G73">
-        <v>-16.37875305784449</v>
+        <v>-17.36805827879983</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.11730835850346</v>
       </c>
       <c r="E74">
-        <v>-28.37530699691987</v>
+        <v>-27.52879482219204</v>
       </c>
       <c r="F74">
-        <v>-3.881056492552844</v>
+        <v>-5.187198149987585</v>
       </c>
       <c r="G74">
-        <v>-16.98917958401239</v>
+        <v>-17.10525889752863</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.18376211790651</v>
       </c>
       <c r="E75">
-        <v>-29.74169025196526</v>
+        <v>-31.9788084892055</v>
       </c>
       <c r="F75">
-        <v>-4.099247615787725</v>
+        <v>-4.715219737509448</v>
       </c>
       <c r="G75">
-        <v>-16.10259893586787</v>
+        <v>-16.56358578112031</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.24614961511625</v>
       </c>
       <c r="E76">
-        <v>-29.65609530050928</v>
+        <v>-29.70755687913244</v>
       </c>
       <c r="F76">
-        <v>-3.822991498869172</v>
+        <v>-4.614162671192299</v>
       </c>
       <c r="G76">
-        <v>-16.53045880718159</v>
+        <v>-17.8945575097289</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.29030981609971</v>
       </c>
       <c r="E77">
-        <v>-28.69439686092235</v>
+        <v>-31.11972074215837</v>
       </c>
       <c r="F77">
-        <v>-4.675464759767129</v>
+        <v>-4.806661333361006</v>
       </c>
       <c r="G77">
-        <v>-16.01377534377646</v>
+        <v>-16.45839816242827</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-15.31524843127473</v>
       </c>
       <c r="E78">
-        <v>-28.65434703679851</v>
+        <v>-29.8978116576167</v>
       </c>
       <c r="F78">
-        <v>-4.354358883176289</v>
+        <v>-4.638498688141899</v>
       </c>
       <c r="G78">
-        <v>-15.48033224357877</v>
+        <v>-16.87312013376939</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-15.321331553362</v>
       </c>
       <c r="E79">
-        <v>-30.26920313217076</v>
+        <v>-33.85551453712328</v>
       </c>
       <c r="F79">
-        <v>-4.36539097858324</v>
+        <v>-5.309696218840911</v>
       </c>
       <c r="G79">
-        <v>-15.68170776291432</v>
+        <v>-15.33112761139658</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-15.29534175046492</v>
       </c>
       <c r="E80">
-        <v>-31.29470550628876</v>
+        <v>-31.14603117614294</v>
       </c>
       <c r="F80">
-        <v>-4.215501132216473</v>
+        <v>-5.313265100121354</v>
       </c>
       <c r="G80">
-        <v>-15.61522704266745</v>
+        <v>-17.51975244122754</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-15.24340420904694</v>
       </c>
       <c r="E81">
-        <v>-30.12327532151059</v>
+        <v>-33.26997831945749</v>
       </c>
       <c r="F81">
-        <v>-4.149021117151114</v>
+        <v>-4.739415596485532</v>
       </c>
       <c r="G81">
-        <v>-16.08352191719782</v>
+        <v>-17.1955407849301</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.16514617118146</v>
       </c>
       <c r="E82">
-        <v>-31.20059023098735</v>
+        <v>-33.59434385567891</v>
       </c>
       <c r="F82">
-        <v>-4.375060295049956</v>
+        <v>-5.017283134173045</v>
       </c>
       <c r="G82">
-        <v>-16.15124574729469</v>
+        <v>-15.0873092429748</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-15.0515056446277</v>
       </c>
       <c r="E83">
-        <v>-29.99780942065408</v>
+        <v>-32.77518592819441</v>
       </c>
       <c r="F83">
-        <v>-4.592975061602592</v>
+        <v>-5.463034584838547</v>
       </c>
       <c r="G83">
-        <v>-15.19749413015836</v>
+        <v>-16.25767813110949</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.91309413973955</v>
       </c>
       <c r="E84">
-        <v>-32.77877700808249</v>
+        <v>-33.83328652245663</v>
       </c>
       <c r="F84">
-        <v>-4.265685605264919</v>
+        <v>-5.233764646872209</v>
       </c>
       <c r="G84">
-        <v>-16.31477345475253</v>
+        <v>-15.81438118594616</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.7511935247261</v>
       </c>
       <c r="E85">
-        <v>-33.57758170913952</v>
+        <v>-34.85376229042612</v>
       </c>
       <c r="F85">
-        <v>-4.626540916627373</v>
+        <v>-5.648828628014241</v>
       </c>
       <c r="G85">
-        <v>-15.59161623188137</v>
+        <v>-17.39325649617199</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.5625572185976</v>
       </c>
       <c r="E86">
-        <v>-33.60489293587977</v>
+        <v>-37.02198205987666</v>
       </c>
       <c r="F86">
-        <v>-4.637489075620807</v>
+        <v>-4.411183043275214</v>
       </c>
       <c r="G86">
-        <v>-15.61805093801245</v>
+        <v>-15.12481110284366</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.36144206297236</v>
       </c>
       <c r="E87">
-        <v>-34.52383805236029</v>
+        <v>-36.21643219678521</v>
       </c>
       <c r="F87">
-        <v>-4.414475567873413</v>
+        <v>-5.224570442180125</v>
       </c>
       <c r="G87">
-        <v>-15.78580786739671</v>
+        <v>-16.38135680191113</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.14751173873597</v>
       </c>
       <c r="E88">
-        <v>-35.13946145133303</v>
+        <v>-36.55864444907085</v>
       </c>
       <c r="F88">
-        <v>-4.124457838402648</v>
+        <v>-5.003359983617459</v>
       </c>
       <c r="G88">
-        <v>-15.52586217638036</v>
+        <v>-15.04245797200875</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.92149116522419</v>
       </c>
       <c r="E89">
-        <v>-36.31510764541235</v>
+        <v>-37.9754771687987</v>
       </c>
       <c r="F89">
-        <v>-4.1934963303744</v>
+        <v>-5.690571948533394</v>
       </c>
       <c r="G89">
-        <v>-16.21689386533844</v>
+        <v>-15.8998561612246</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.69329923137322</v>
       </c>
       <c r="E90">
-        <v>-38.00646098795918</v>
+        <v>-40.4530913394013</v>
       </c>
       <c r="F90">
-        <v>-4.352212961660868</v>
+        <v>-4.581935047666065</v>
       </c>
       <c r="G90">
-        <v>-15.73729347779146</v>
+        <v>-17.61173263849065</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.45758820136554</v>
       </c>
       <c r="E91">
-        <v>-38.54382556336837</v>
+        <v>-39.36993922692864</v>
       </c>
       <c r="F91">
-        <v>-4.378719447567578</v>
+        <v>-4.937668654097989</v>
       </c>
       <c r="G91">
-        <v>-16.00841888109392</v>
+        <v>-16.10622232796061</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.21569259837723</v>
       </c>
       <c r="E92">
-        <v>-39.82962688768427</v>
+        <v>-39.82708414952896</v>
       </c>
       <c r="F92">
-        <v>-4.438709435791467</v>
+        <v>-5.082049579437898</v>
       </c>
       <c r="G92">
-        <v>-16.17260207656853</v>
+        <v>-16.75610393586555</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.97045378849442</v>
       </c>
       <c r="E93">
-        <v>-41.29378442502927</v>
+        <v>-42.51004197400938</v>
       </c>
       <c r="F93">
-        <v>-4.544477235354091</v>
+        <v>-4.823052689585804</v>
       </c>
       <c r="G93">
-        <v>-16.06941899320053</v>
+        <v>-17.19178000519748</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.70871152495819</v>
       </c>
       <c r="E94">
-        <v>-43.02870168752988</v>
+        <v>-43.10127274773981</v>
       </c>
       <c r="F94">
-        <v>-4.476038176071333</v>
+        <v>-5.120115534821402</v>
       </c>
       <c r="G94">
-        <v>-15.76886780587225</v>
+        <v>-18.30641420390578</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.43183562376436</v>
       </c>
       <c r="E95">
-        <v>-44.2770864953574</v>
+        <v>-44.21589775456576</v>
       </c>
       <c r="F95">
-        <v>-4.229813082574299</v>
+        <v>-4.629788305606983</v>
       </c>
       <c r="G95">
-        <v>-15.57190358846778</v>
+        <v>-16.37661775597166</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.13527152572443</v>
       </c>
       <c r="E96">
-        <v>-45.96342002446673</v>
+        <v>-48.11476443552768</v>
       </c>
       <c r="F96">
-        <v>-4.5822977163207</v>
+        <v>-4.575596264739517</v>
       </c>
       <c r="G96">
-        <v>-15.41934371838154</v>
+        <v>-15.84443431835166</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.81132583980457</v>
       </c>
       <c r="E97">
-        <v>-47.05102362688891</v>
+        <v>-48.37605965000727</v>
       </c>
       <c r="F97">
-        <v>-4.254589369768392</v>
+        <v>-4.769549560791556</v>
       </c>
       <c r="G97">
-        <v>-16.36000212791006</v>
+        <v>-16.35625293508683</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.46278125498897</v>
       </c>
       <c r="E98">
-        <v>-49.4858267363415</v>
+        <v>-50.00793375070035</v>
       </c>
       <c r="F98">
-        <v>-4.776045130603731</v>
+        <v>-4.776096601045983</v>
       </c>
       <c r="G98">
-        <v>-15.25442558179721</v>
+        <v>-16.87940189393016</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.10294446566769</v>
       </c>
       <c r="E99">
-        <v>-51.21814805111722</v>
+        <v>-51.30139498880022</v>
       </c>
       <c r="F99">
-        <v>-4.91622131673815</v>
+        <v>-4.460396704597494</v>
       </c>
       <c r="G99">
-        <v>-16.85023267718364</v>
+        <v>-16.41858885231854</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.71872503896656</v>
       </c>
       <c r="E100">
-        <v>-52.86904400687951</v>
+        <v>-53.13572810542823</v>
       </c>
       <c r="F100">
-        <v>-4.646962012554008</v>
+        <v>-4.738461413671479</v>
       </c>
       <c r="G100">
-        <v>-16.13566631998689</v>
+        <v>-18.3973416476874</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.34996630403203</v>
       </c>
       <c r="E101">
-        <v>-53.44944040654659</v>
+        <v>-55.77579448834499</v>
       </c>
       <c r="F101">
-        <v>-4.680820061320188</v>
+        <v>-5.377270574693839</v>
       </c>
       <c r="G101">
-        <v>-15.63847534871698</v>
+        <v>-17.56747395517613</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.963340514015552</v>
       </c>
       <c r="E102">
-        <v>-55.26747214886549</v>
+        <v>-55.83473937026583</v>
       </c>
       <c r="F102">
-        <v>-4.412359736770386</v>
+        <v>-4.588788535015128</v>
       </c>
       <c r="G102">
-        <v>-16.10735453453504</v>
+        <v>-17.01727783927696</v>
       </c>
     </row>
   </sheetData>
